--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2018_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2018_tarapaca.xlsx
@@ -459,7 +459,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -468,36 +468,25 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>257668</v>
+          <t>Camiña</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Camiña</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>94447.77</v>
+          <t>Colchane</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Colchane</t>
+          <t>Pozo Almonte</t>
         </is>
       </c>
     </row>
@@ -507,38 +496,26 @@
           <t>Huara</t>
         </is>
       </c>
-      <c r="B5">
-        <v>171958.84</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Iquique</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>356839.47</v>
+          <t>Alto Hospicio</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pica</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>220055.06</v>
+          <t>Iquique</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>290526.81</v>
+          <t>Pica</t>
+        </is>
       </c>
     </row>
   </sheetData>
